--- a/reports/剩余持仓_2026-08.xlsx
+++ b/reports/剩余持仓_2026-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,26 +494,107 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>300308</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" t="n">
+        <v>98100</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>300502</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="n">
+        <v>42138</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>300548</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>688041</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>海光信息</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>400</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F6" t="n">
         <v>108036</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-08.xlsx
+++ b/reports/剩余持仓_2026-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,65 +467,65 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2594</v>
+        <v>2384</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
         <v>100</v>
       </c>
-      <c r="D2" t="n">
-        <v>9122</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>18339</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>300308</v>
+        <v>2594</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>72715</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>98100</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 800股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>300502</v>
+        <v>300308</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -535,24 +535,24 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F4" t="n">
-        <v>42138</v>
+        <v>189100</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>300548</v>
+        <v>300394</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>长芯博创</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -565,7 +565,7 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>15100</v>
+        <v>20190</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -575,26 +575,80 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>300502</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>300</v>
+      </c>
+      <c r="F6" t="n">
+        <v>123114</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>300548</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" t="n">
+        <v>30767</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>688041</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>海光信息</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>400</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F8" t="n">
         <v>108036</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-08.xlsx
+++ b/reports/剩余持仓_2026-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,26 +629,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>688008</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D8" t="n">
+        <v>126052.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 600股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>688041</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>海光信息</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>400</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>108036</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-08.xlsx
+++ b/reports/剩余持仓_2026-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,65 +467,65 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2384</v>
+        <v>988</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>10771</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>18339</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 100股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2594</v>
+        <v>2156</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>72715</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>12314</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>仅买入未平仓 800股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>300308</v>
+        <v>2384</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -535,51 +535,51 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>189100</v>
+        <v>18339</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>300394</v>
+        <v>2594</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>72715</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>20190</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 800股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>300502</v>
+        <v>300308</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -589,24 +589,24 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F6" t="n">
-        <v>123114</v>
+        <v>189100</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>300548</v>
+        <v>300394</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>长芯博创</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -616,68 +616,149 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>30767</v>
+        <v>20190</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>688008</v>
+        <v>300502</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>126052.5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>123114</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅买入未平仓 600股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>300548</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30767</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>300750</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>38752</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>688041</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>海光信息</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>400</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>108036</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>688778</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>厦钨新能</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>300</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14055</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-08.xlsx
+++ b/reports/剩余持仓_2026-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -710,53 +710,107 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>688041</v>
+        <v>512760</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>11410</v>
       </c>
       <c r="E11" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>108036</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 10000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>561980</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10875</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 15000股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>688041</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>400</v>
+      </c>
+      <c r="F13" t="n">
+        <v>108036</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>688778</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>厦钨新能</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
         <v>300</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F14" t="n">
         <v>14055</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-08.xlsx
+++ b/reports/剩余持仓_2026-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,18 +467,18 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>988</v>
+        <v>831</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>中国稀土</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>10771</v>
+        <v>11404</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -488,44 +488,44 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2156</v>
+        <v>988</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>10771</v>
       </c>
       <c r="E3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>12314</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 100股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2384</v>
+        <v>2156</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -535,132 +535,132 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F4" t="n">
-        <v>18339</v>
+        <v>12314</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2594</v>
+        <v>2384</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>72715</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>18339</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>仅买入未平仓 800股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>300308</v>
+        <v>2436</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>兴森科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>16960</v>
       </c>
       <c r="E6" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>189100</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 500股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>300394</v>
+        <v>2594</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>72715</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>20190</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 800股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>300502</v>
+        <v>300054</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>鼎龙股份</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>15574</v>
       </c>
       <c r="E8" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>123114</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>300548</v>
+        <v>300308</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>长芯博创</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -673,7 +673,7 @@
         <v>200</v>
       </c>
       <c r="F9" t="n">
-        <v>30767</v>
+        <v>189100</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>300750</v>
+        <v>300394</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -700,7 +700,7 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>38752</v>
+        <v>20190</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -710,65 +710,65 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>512760</v>
+        <v>300502</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>11410</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>123114</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>仅买入未平仓 10000股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>561980</v>
+        <v>300548</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>芯片设备</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>10875</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>30767</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>仅买入未平仓 15000股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>688041</v>
+        <v>300750</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -778,39 +778,120 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>108036</v>
+        <v>38752</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>512760</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17095</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 15000股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>561980</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>15914</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 22000股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>688041</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>200</v>
+      </c>
+      <c r="F16" t="n">
+        <v>54018</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>；仍卖出未平仓 200股</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>688778</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>厦钨新能</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
         <v>300</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F17" t="n">
         <v>14055</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-08.xlsx
+++ b/reports/剩余持仓_2026-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D2" t="n">
-        <v>11404</v>
+        <v>17051</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -845,53 +845,107 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>688041</v>
+        <v>600259</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>中稀有色</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>8928</v>
       </c>
       <c r="E16" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>54018</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>仅买入未平仓 100股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>688008</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>200</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42715.5</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>；仍卖出未平仓 200股</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>688041</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>400</v>
+      </c>
+      <c r="F18" t="n">
+        <v>110428.67</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>；仍卖出未平仓 400股</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>688778</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>厦钨新能</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
         <v>300</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F19" t="n">
         <v>14055</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-08.xlsx
+++ b/reports/剩余持仓_2026-08.xlsx
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="D15" t="n">
-        <v>15914</v>
+        <v>17374</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仅买入未平仓 22000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 24000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -872,28 +872,28 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>688008</v>
+        <v>601208</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>9804</v>
       </c>
       <c r="E17" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>42715.5</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-08.xlsx
+++ b/reports/剩余持仓_2026-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,38 +494,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>988</v>
+        <v>2156</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>10771</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>12314</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2156</v>
+        <v>2384</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -535,58 +535,58 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>12314</v>
+        <v>18339</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2384</v>
+        <v>2436</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>兴森科技</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>16960</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>18339</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 500股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2436</v>
+        <v>2594</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="D6" t="n">
-        <v>16960</v>
+        <v>72715</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -596,24 +596,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仅买入未平仓 500股（跨期持有底仓）</t>
+          <t>仅买入未平仓 800股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2594</v>
+        <v>300054</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>鼎龙股份</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="D7" t="n">
-        <v>72715</v>
+        <v>15574</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -623,44 +623,44 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅买入未平仓 800股（跨期持有底仓）</t>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>300054</v>
+        <v>300308</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>鼎龙股份</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>200</v>
       </c>
-      <c r="D8" t="n">
-        <v>15574</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>189100</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>300308</v>
+        <v>300394</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -670,24 +670,24 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>189100</v>
+        <v>20190</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>300394</v>
+        <v>300502</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -697,24 +697,24 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F10" t="n">
-        <v>20190</v>
+        <v>123114</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>300502</v>
+        <v>300548</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -724,24 +724,24 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F11" t="n">
-        <v>123114</v>
+        <v>30767</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>300548</v>
+        <v>300750</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>长芯博创</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -751,58 +751,58 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>30767</v>
+        <v>38752</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>300750</v>
+        <v>512760</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>20518</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>38752</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 18000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>512760</v>
+        <v>561980</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>芯片设备</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15000</v>
+        <v>28000</v>
       </c>
       <c r="D14" t="n">
-        <v>17095</v>
+        <v>20238</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -812,24 +812,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>仅买入未平仓 15000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 28000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>561980</v>
+        <v>600259</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>芯片设备</t>
+          <t>中稀有色</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24000</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>17374</v>
+        <v>8928</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -839,24 +839,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仅买入未平仓 24000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 100股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>600259</v>
+        <v>601208</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中稀有色</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D16" t="n">
-        <v>8928</v>
+        <v>9804</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -866,44 +866,44 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>601208</v>
+        <v>688041</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9804</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>110428.67</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>；仍卖出未平仓 400股</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>688041</v>
+        <v>688778</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>厦钨新能</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -913,39 +913,12 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F18" t="n">
-        <v>110428.67</v>
+        <v>14055</v>
       </c>
       <c r="G18" t="inlineStr">
-        <is>
-          <t>；仍卖出未平仓 400股</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>688778</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>厦钨新能</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>300</v>
-      </c>
-      <c r="F19" t="n">
-        <v>14055</v>
-      </c>
-      <c r="G19" t="inlineStr">
         <is>
           <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-08.xlsx
+++ b/reports/剩余持仓_2026-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="D2" t="n">
-        <v>17051</v>
+        <v>29251</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -488,44 +488,44 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 300股（跨期持有底仓）</t>
+          <t>仅买入未平仓 500股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2156</v>
+        <v>988</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>11035.5</v>
       </c>
       <c r="E3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>12314</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2384</v>
+        <v>2156</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -538,28 +538,28 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>18339</v>
+        <v>6157</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2436</v>
+        <v>2222</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>16960</v>
+        <v>6156</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -569,51 +569,51 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>仅买入未平仓 500股（跨期持有底仓）</t>
+          <t>仅买入未平仓 100股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2594</v>
+        <v>2384</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>72715</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>18339</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仅买入未平仓 800股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>300054</v>
+        <v>2436</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>鼎龙股份</t>
+          <t>兴森科技</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="D7" t="n">
-        <v>15574</v>
+        <v>16960</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -623,44 +623,44 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仅买入未平仓 500股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>300308</v>
+        <v>2594</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>90967</v>
       </c>
       <c r="E8" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>189100</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 1000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>300394</v>
+        <v>300308</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -670,24 +670,24 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F9" t="n">
-        <v>20190</v>
+        <v>189100</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>300502</v>
+        <v>300394</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -697,24 +697,24 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>123114</v>
+        <v>20190</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>300548</v>
+        <v>300502</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>长芯博创</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -724,24 +724,24 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F11" t="n">
-        <v>30767</v>
+        <v>123114</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>300750</v>
+        <v>300548</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -751,58 +751,58 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F12" t="n">
-        <v>38752</v>
+        <v>52364</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>512760</v>
+        <v>300750</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>20518</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>38752</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>仅买入未平仓 18000股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>561980</v>
+        <v>512760</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>芯片设备</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28000</v>
+        <v>20000</v>
       </c>
       <c r="D14" t="n">
-        <v>20238</v>
+        <v>22277.14</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -812,24 +812,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>仅买入未平仓 28000股（跨期持有底仓）</t>
+          <t>仍买入未平仓 20000股</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>600259</v>
+        <v>561980</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中稀有色</t>
+          <t>芯片设备</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>100</v>
+        <v>40000</v>
       </c>
       <c r="D15" t="n">
-        <v>8928</v>
+        <v>28315</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -839,24 +839,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仍买入未平仓 40000股</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>601208</v>
+        <v>600259</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>中稀有色</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D16" t="n">
-        <v>9804</v>
+        <v>17539</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -866,59 +866,113 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>688041</v>
+        <v>600498</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>16476</v>
       </c>
       <c r="E17" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>110428.67</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 400股</t>
+          <t>仅买入未平仓 400股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>601208</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>300</v>
+      </c>
+      <c r="D18" t="n">
+        <v>14141</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>688041</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>200</v>
+      </c>
+      <c r="F19" t="n">
+        <v>55214.33</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>；仍卖出未平仓 200股</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>688778</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>厦钨新能</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
         <v>300</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F20" t="n">
         <v>14055</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-08.xlsx
+++ b/reports/剩余持仓_2026-08.xlsx
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D7" t="n">
-        <v>16960</v>
+        <v>20558</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -623,7 +623,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅买入未平仓 500股（跨期持有底仓）</t>
+          <t>仅买入未平仓 600股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="D8" t="n">
-        <v>90967</v>
+        <v>72773.60000000001</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅买入未平仓 1000股（跨期持有底仓）</t>
+          <t>仍买入未平仓 800股</t>
         </is>
       </c>
     </row>
@@ -751,58 +751,58 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F12" t="n">
-        <v>52364</v>
+        <v>34909.33</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>300750</v>
+        <v>512760</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>30058.71</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>38752</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仍买入未平仓 27000股</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>512760</v>
+        <v>561980</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>芯片设备</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="D14" t="n">
-        <v>22277.14</v>
+        <v>35317.24</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -812,24 +812,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>仍买入未平仓 20000股</t>
+          <t>仍买入未平仓 50000股</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>561980</v>
+        <v>600259</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>芯片设备</t>
+          <t>中稀有色</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>40000</v>
+        <v>300</v>
       </c>
       <c r="D15" t="n">
-        <v>28315</v>
+        <v>17539</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -839,24 +839,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仍买入未平仓 40000股</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>600259</v>
+        <v>600498</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中稀有色</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="D16" t="n">
-        <v>17539</v>
+        <v>20623</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -866,24 +866,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>仅买入未平仓 300股（跨期持有底仓）</t>
+          <t>仅买入未平仓 500股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>600498</v>
+        <v>601208</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="D17" t="n">
-        <v>16476</v>
+        <v>14141</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -893,24 +893,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨期持有底仓）</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>601208</v>
+        <v>688008</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D18" t="n">
-        <v>14141</v>
+        <v>42854.66</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>仅买入未平仓 300股（跨期持有底仓）</t>
+          <t>仍买入未平仓 200股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-08.xlsx
+++ b/reports/剩余持仓_2026-08.xlsx
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="D8" t="n">
-        <v>72773.60000000001</v>
+        <v>99791.14999999999</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仍买入未平仓 800股</t>
+          <t>仍买入未平仓 1100股</t>
         </is>
       </c>
     </row>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="D16" t="n">
-        <v>20623</v>
+        <v>29033</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>仅买入未平仓 500股（跨期持有底仓）</t>
+          <t>仅买入未平仓 700股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D18" t="n">
-        <v>42854.66</v>
+        <v>85011.75999999999</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>仍买入未平仓 200股</t>
+          <t>仍买入未平仓 400股</t>
         </is>
       </c>
     </row>
